--- a/Backtest/01-03-22/S&P500stock_01-03-22period252RS90.xlsx
+++ b/Backtest/01-03-22/S&P500stock_01-03-22period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="106">
   <si>
     <t>Stock</t>
   </si>
@@ -127,127 +127,211 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>OXY</t>
-  </si>
-  <si>
-    <t>CVX</t>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>REG</t>
   </si>
   <si>
     <t>DVN</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>NUE</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>MOS</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>HES</t>
-  </si>
-  <si>
-    <t>EXC</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>2022-05-05</t>
-  </si>
-  <si>
-    <t>2022-05-10</t>
-  </si>
-  <si>
-    <t>2022-04-29</t>
-  </si>
-  <si>
-    <t>2022-05-02</t>
-  </si>
-  <si>
-    <t>2022-05-04</t>
-  </si>
-  <si>
-    <t>2022-04-19</t>
-  </si>
-  <si>
-    <t>2022-04-21</t>
-  </si>
-  <si>
-    <t>2022-04-28</t>
-  </si>
-  <si>
-    <t>2022-04-27</t>
-  </si>
-  <si>
-    <t>2022-05-09</t>
-  </si>
-  <si>
-    <t>2022-05-19</t>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>KLAC</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>LYV</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>LKQ</t>
+  </si>
+  <si>
+    <t>SPG</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>AZO</t>
+  </si>
+  <si>
+    <t>EXR</t>
+  </si>
+  <si>
+    <t>EPAM</t>
+  </si>
+  <si>
+    <t>CBRE</t>
+  </si>
+  <si>
+    <t>PLD</t>
+  </si>
+  <si>
+    <t>PSA</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>TSCO</t>
+  </si>
+  <si>
+    <t>2022-01-27</t>
+  </si>
+  <si>
+    <t>2022-02-10</t>
+  </si>
+  <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
+    <t>2022-03-01</t>
+  </si>
+  <si>
+    <t>2022-02-07</t>
+  </si>
+  <si>
+    <t>2022-02-03</t>
+  </si>
+  <si>
+    <t>2022-02-16</t>
+  </si>
+  <si>
+    <t>2022-02-08</t>
+  </si>
+  <si>
+    <t>2022-02-23</t>
+  </si>
+  <si>
+    <t>2022-02-17</t>
+  </si>
+  <si>
+    <t>2022-01-26</t>
+  </si>
+  <si>
+    <t>2022-02-02</t>
+  </si>
+  <si>
+    <t>2022-02-24</t>
+  </si>
+  <si>
+    <t>2022-01-19</t>
+  </si>
+  <si>
+    <t>2022-02-22</t>
+  </si>
+  <si>
+    <t>2022-03-16</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Utilities</t>
-  </si>
-  <si>
     <t>Technology</t>
   </si>
   <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>REIT - Retail</t>
+  </si>
+  <si>
     <t>Oil &amp; Gas E&amp;P</t>
   </si>
   <si>
-    <t>Oil &amp; Gas Integrated</t>
-  </si>
-  <si>
-    <t>Agricultural Inputs</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Utilities - Regulated Electric</t>
-  </si>
-  <si>
-    <t>Software - Infrastructure</t>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Specialty Retail</t>
+  </si>
+  <si>
+    <t>REIT - Industrial</t>
+  </si>
+  <si>
+    <t>Real Estate Services</t>
+  </si>
+  <si>
+    <t>REIT - Residential</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
   </si>
 </sst>
 </file>
@@ -605,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -726,49 +810,49 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>98.18548387096774</v>
+        <v>98.7878787878788</v>
       </c>
       <c r="C2">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="D2">
-        <v>114.92</v>
+        <v>114.15</v>
       </c>
       <c r="E2">
-        <v>2.39</v>
+        <v>3.15</v>
       </c>
       <c r="F2">
-        <v>-0.5069857671590039</v>
+        <v>0.8960609666144673</v>
       </c>
       <c r="G2">
-        <v>2.18</v>
+        <v>2.72</v>
       </c>
       <c r="H2">
-        <v>-0.5943849614362987</v>
+        <v>0.8058810291824892</v>
       </c>
       <c r="I2">
-        <v>110.431999206543</v>
+        <v>114.7979995727539</v>
       </c>
       <c r="J2">
-        <v>112.2229999542236</v>
+        <v>113.666499710083</v>
       </c>
       <c r="K2">
-        <v>102.8689996337891</v>
+        <v>111.9767997741699</v>
       </c>
       <c r="L2">
-        <v>86.76454967498779</v>
+        <v>101.820599822998</v>
       </c>
       <c r="M2">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -777,58 +861,58 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>62.81</v>
+        <v>47.94</v>
       </c>
       <c r="Y2">
-        <v>116.97</v>
+        <v>128.81</v>
       </c>
       <c r="Z2">
-        <v>51.88</v>
+        <v>28.68</v>
       </c>
       <c r="AA2">
-        <v>-43.12</v>
+        <v>166.14</v>
       </c>
       <c r="AB2">
-        <v>6076.92</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="AC2">
-        <v>192.31</v>
+        <v>456.49</v>
       </c>
       <c r="AD2">
-        <v>8.949999999999999</v>
+        <v>15.94</v>
       </c>
       <c r="AE2">
-        <v>81.91</v>
+        <v>44.36</v>
       </c>
       <c r="AF2">
-        <v>20.51</v>
+        <v>62.9</v>
       </c>
       <c r="AG2">
-        <v>33.33</v>
+        <v>136.64</v>
       </c>
       <c r="AH2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AI2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="AK2">
-        <v>82.26981155929548</v>
+        <v>89.33571637428572</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -836,58 +920,58 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.16935483870968</v>
+        <v>91.31313131313131</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>348</v>
       </c>
       <c r="D3">
-        <v>43.73</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="E3">
-        <v>3.78</v>
+        <v>1.31</v>
       </c>
       <c r="F3">
-        <v>1.159227539929628</v>
+        <v>-1.006626855970358</v>
       </c>
       <c r="G3">
-        <v>3.41</v>
+        <v>1.49</v>
       </c>
       <c r="H3">
-        <v>1.098883368758934</v>
+        <v>-0.908827907161889</v>
       </c>
       <c r="I3">
-        <v>39.67999954223633</v>
+        <v>74.36800079345703</v>
       </c>
       <c r="J3">
-        <v>40.01199970245361</v>
+        <v>73.00650024414062</v>
       </c>
       <c r="K3">
-        <v>35.46579982757569</v>
+        <v>72.80380004882812</v>
       </c>
       <c r="L3">
-        <v>30.53310000419617</v>
+        <v>66.75415008544923</v>
       </c>
       <c r="M3">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>6.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -896,49 +980,49 @@
         <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>21.62</v>
+        <v>43.49</v>
       </c>
       <c r="Y3">
-        <v>43.78</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="Z3">
-        <v>27.8</v>
+        <v>11.49</v>
       </c>
       <c r="AA3">
-        <v>-90</v>
+        <v>15.2</v>
       </c>
       <c r="AB3">
-        <v>109.29</v>
+        <v>286.27</v>
       </c>
       <c r="AC3">
-        <v>483.78</v>
+        <v>187.5</v>
       </c>
       <c r="AD3">
-        <v>14.78</v>
+        <v>1.93</v>
       </c>
       <c r="AE3">
-        <v>111.94</v>
+        <v>23.21</v>
       </c>
       <c r="AF3">
-        <v>770</v>
+        <v>16.67</v>
       </c>
       <c r="AG3">
-        <v>72.97</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="AI3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AK3">
-        <v>71.06036895932021</v>
+        <v>74.04104327809561</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -946,43 +1030,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>90.7258064516129</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>144</v>
+        <v>44.05</v>
       </c>
       <c r="E4">
-        <v>1.68</v>
+        <v>3.55</v>
       </c>
       <c r="F4">
-        <v>-1.358073139844564</v>
+        <v>1.309688754132907</v>
       </c>
       <c r="G4">
-        <v>1.51</v>
+        <v>2.98</v>
       </c>
       <c r="H4">
-        <v>-1.516734377071101</v>
+        <v>1.168339828734959</v>
       </c>
       <c r="I4">
-        <v>137.4360015869141</v>
+        <v>44.20599975585937</v>
       </c>
       <c r="J4">
-        <v>135.9339996337891</v>
+        <v>42.28899993896484</v>
       </c>
       <c r="K4">
-        <v>128.4024002075195</v>
+        <v>42.19000015258789</v>
       </c>
       <c r="L4">
-        <v>111.5214500427246</v>
+        <v>31.5247500705719</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1006,49 +1090,49 @@
         <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4">
-        <v>92.86</v>
+        <v>15.71</v>
       </c>
       <c r="Y4">
-        <v>144</v>
+        <v>45.56</v>
       </c>
       <c r="Z4">
-        <v>225.31</v>
+        <v>24.11</v>
       </c>
       <c r="AA4">
-        <v>121.14</v>
+        <v>-0.38</v>
       </c>
       <c r="AB4">
-        <v>463.84</v>
+        <v>119.22</v>
       </c>
       <c r="AC4">
-        <v>265.28</v>
+        <v>559.26</v>
       </c>
       <c r="AD4">
-        <v>3.63</v>
+        <v>9.31</v>
       </c>
       <c r="AE4">
-        <v>-17.55</v>
+        <v>226.32</v>
       </c>
       <c r="AF4">
-        <v>98.14</v>
+        <v>15.15</v>
       </c>
       <c r="AG4">
-        <v>123.61</v>
+        <v>222.22</v>
       </c>
       <c r="AH4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="AI4" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AK4">
-        <v>66.78449528232775</v>
+        <v>71.52599817378861</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1056,49 +1140,49 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>98.58585858585859</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="D5">
-        <v>59.55</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E5">
-        <v>3.08</v>
+        <v>2.22</v>
       </c>
       <c r="F5">
-        <v>0.3201273133382307</v>
+        <v>-0.06562363936590616</v>
       </c>
       <c r="G5">
-        <v>3.11</v>
+        <v>2.17</v>
       </c>
       <c r="H5">
-        <v>0.6858910931015599</v>
+        <v>0.03914126089841737</v>
       </c>
       <c r="I5">
-        <v>54.74399948120117</v>
+        <v>84.71600036621093</v>
       </c>
       <c r="J5">
-        <v>53.28799953460693</v>
+        <v>79.06600036621094</v>
       </c>
       <c r="K5">
-        <v>49.28599983215332</v>
+        <v>71.19100006103515</v>
       </c>
       <c r="L5">
-        <v>37.05465001106262</v>
+        <v>53.93020002365112</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1107,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1116,49 +1200,49 @@
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>20.14</v>
+        <v>37.46</v>
       </c>
       <c r="Y5">
-        <v>59.66</v>
+        <v>86.2</v>
       </c>
       <c r="Z5">
-        <v>29.29</v>
+        <v>10.64</v>
       </c>
       <c r="AA5">
-        <v>-36.84</v>
+        <v>104.94</v>
       </c>
       <c r="AB5">
-        <v>161.86</v>
+        <v>144.41</v>
       </c>
       <c r="AC5">
-        <v>581.8200000000001</v>
+        <v>152.1</v>
       </c>
       <c r="AD5">
-        <v>16.09</v>
+        <v>11.1</v>
       </c>
       <c r="AE5">
-        <v>81.45</v>
+        <v>25</v>
       </c>
       <c r="AF5">
-        <v>226.32</v>
+        <v>185.71</v>
       </c>
       <c r="AG5">
-        <v>15.15</v>
+        <v>-29.41</v>
       </c>
       <c r="AH5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="AI5" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AK5">
-        <v>65.0385399019988</v>
+        <v>71.24636782195689</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1166,43 +1250,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>98.38709677419355</v>
+        <v>98.18181818181819</v>
       </c>
       <c r="C6">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="D6">
-        <v>81.19</v>
+        <v>67.92</v>
       </c>
       <c r="E6">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="F6">
-        <v>0.6797416961631151</v>
+        <v>1.144237639125532</v>
       </c>
       <c r="G6">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="H6">
-        <v>0.36926368176424</v>
+        <v>1.461095012988877</v>
       </c>
       <c r="I6">
-        <v>77.51200103759766</v>
+        <v>68.51199951171876</v>
       </c>
       <c r="J6">
-        <v>74.54500007629395</v>
+        <v>64.92349987030029</v>
       </c>
       <c r="K6">
-        <v>71.19100006103515</v>
+        <v>60.12980003356934</v>
       </c>
       <c r="L6">
-        <v>58.04500011444092</v>
+        <v>45.9561999130249</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1211,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6">
         <v>3.333333333333333</v>
@@ -1226,49 +1310,49 @@
         <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>43.19</v>
+        <v>32.32</v>
       </c>
       <c r="Y6">
-        <v>81.22</v>
+        <v>70.27</v>
       </c>
       <c r="Z6">
-        <v>15.3</v>
+        <v>20.17</v>
       </c>
       <c r="AA6">
-        <v>-51.32</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="AB6">
-        <v>95.87</v>
+        <v>122.54</v>
       </c>
       <c r="AC6">
-        <v>370</v>
+        <v>242.86</v>
       </c>
       <c r="AD6">
-        <v>14.23</v>
+        <v>7.49</v>
       </c>
       <c r="AE6">
-        <v>482.56</v>
+        <v>67.44</v>
       </c>
       <c r="AF6">
-        <v>-175.44</v>
+        <v>95.45</v>
       </c>
       <c r="AG6">
-        <v>62.86</v>
+        <v>4.76</v>
       </c>
       <c r="AH6" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AI6" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="AK6">
-        <v>63.74647157504693</v>
+        <v>69.66053372567374</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1276,40 +1360,40 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>98.79032258064517</v>
+        <v>99.39393939393939</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>94.86</v>
+        <v>20.77</v>
       </c>
       <c r="E7">
-        <v>1.97</v>
+        <v>3.07</v>
       </c>
       <c r="F7">
-        <v>-1.010445903113843</v>
+        <v>0.8133354091107792</v>
       </c>
       <c r="G7">
-        <v>2.1</v>
+        <v>2.83</v>
       </c>
       <c r="H7">
-        <v>-0.7045162349449319</v>
+        <v>0.9592289828393032</v>
       </c>
       <c r="I7">
-        <v>89.98400115966797</v>
+        <v>20.67199974060059</v>
       </c>
       <c r="J7">
-        <v>90.99550094604493</v>
+        <v>20.13599987030029</v>
       </c>
       <c r="K7">
-        <v>83.79180023193359</v>
+        <v>19.32940000534058</v>
       </c>
       <c r="L7">
-        <v>68.48469999313355</v>
+        <v>14.98689998149872</v>
       </c>
       <c r="M7">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
         <v>1.07</v>
@@ -1336,49 +1420,49 @@
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>47.85</v>
+        <v>8.43</v>
       </c>
       <c r="Y7">
-        <v>95.06999999999999</v>
+        <v>21.49</v>
       </c>
       <c r="Z7">
-        <v>95.87</v>
+        <v>57.15</v>
       </c>
       <c r="AA7">
-        <v>-20.46</v>
+        <v>5.35</v>
       </c>
       <c r="AB7">
-        <v>446.02</v>
+        <v>196</v>
       </c>
       <c r="AC7">
-        <v>168</v>
+        <v>165.71</v>
       </c>
       <c r="AD7">
-        <v>5.79</v>
+        <v>4.96</v>
       </c>
       <c r="AE7">
-        <v>12.92</v>
+        <v>228.57</v>
       </c>
       <c r="AF7">
-        <v>14.84</v>
+        <v>-82.93000000000001</v>
       </c>
       <c r="AG7">
-        <v>106.67</v>
+        <v>217.14</v>
       </c>
       <c r="AH7" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AI7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="AJ7" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="AK7">
-        <v>63.33026711877594</v>
+        <v>69.55875155742629</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1386,43 +1470,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>93.34677419354838</v>
+        <v>99.19191919191918</v>
       </c>
       <c r="C8">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>33.53</v>
+        <v>29.41</v>
       </c>
       <c r="E8">
-        <v>2.27</v>
+        <v>4.05</v>
       </c>
       <c r="F8">
-        <v>-0.6508315202889579</v>
+        <v>1.826723488530958</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>3.59</v>
       </c>
       <c r="H8">
-        <v>-0.2639911409103999</v>
+        <v>2.018723935377293</v>
       </c>
       <c r="I8">
-        <v>32.13399925231933</v>
+        <v>30.05299987792969</v>
       </c>
       <c r="J8">
-        <v>32.1939998626709</v>
+        <v>29.7457498550415</v>
       </c>
       <c r="K8">
-        <v>28.42999996185303</v>
+        <v>29.29789978027344</v>
       </c>
       <c r="L8">
-        <v>23.84634998321533</v>
+        <v>21.07971370220184</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1434,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1446,49 +1530,49 @@
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>17.82</v>
+        <v>11.57</v>
       </c>
       <c r="Y8">
-        <v>34.32</v>
+        <v>34.65</v>
       </c>
       <c r="Z8">
-        <v>20.4</v>
+        <v>648.89</v>
       </c>
       <c r="AA8">
-        <v>-0.72</v>
+        <v>875.84</v>
       </c>
       <c r="AB8">
-        <v>151.75</v>
+        <v>53.67</v>
       </c>
       <c r="AC8">
-        <v>384.21</v>
+        <v>65.83</v>
       </c>
       <c r="AD8">
-        <v>12.29</v>
+        <v>10.35</v>
       </c>
       <c r="AE8">
-        <v>253.85</v>
+        <v>4.21</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>23.38</v>
       </c>
       <c r="AG8">
-        <v>36.84</v>
+        <v>28.98</v>
       </c>
       <c r="AH8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="AI8" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ8" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="AK8">
-        <v>61.69602145973212</v>
+        <v>59.3183680512122</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1496,43 +1580,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>99.79838709677419</v>
+        <v>92.12121212121212</v>
       </c>
       <c r="C9">
-        <v>191</v>
+        <v>318</v>
       </c>
       <c r="D9">
-        <v>131.62</v>
+        <v>430.11</v>
       </c>
       <c r="E9">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="F9">
-        <v>0.02044866098416014</v>
+        <v>0.3376634534645728</v>
       </c>
       <c r="G9">
-        <v>3.16</v>
+        <v>2.2</v>
       </c>
       <c r="H9">
-        <v>0.754723139044456</v>
+        <v>0.08096343007754889</v>
       </c>
       <c r="I9">
-        <v>123.8520004272461</v>
+        <v>432.9179931640625</v>
       </c>
       <c r="J9">
-        <v>117.7920009613037</v>
+        <v>412.6069961547852</v>
       </c>
       <c r="K9">
-        <v>112.8312002563477</v>
+        <v>402.0789990234375</v>
       </c>
       <c r="L9">
-        <v>107.7016998291016</v>
+        <v>345.1305502319336</v>
       </c>
       <c r="M9">
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1556,49 +1640,49 @@
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>59.46</v>
+        <v>257.7</v>
       </c>
       <c r="Y9">
-        <v>134.38</v>
+        <v>442.44</v>
       </c>
       <c r="Z9">
-        <v>33.49</v>
+        <v>51.32</v>
       </c>
       <c r="AA9">
-        <v>36.05</v>
+        <v>8.4</v>
       </c>
       <c r="AB9">
-        <v>324.68</v>
+        <v>58.13</v>
       </c>
       <c r="AC9">
-        <v>151.29</v>
+        <v>136.82</v>
       </c>
       <c r="AD9">
-        <v>16.02</v>
+        <v>27.69</v>
       </c>
       <c r="AE9">
-        <v>6.86</v>
+        <v>69.73</v>
       </c>
       <c r="AF9">
-        <v>44.36</v>
+        <v>11.92</v>
       </c>
       <c r="AG9">
-        <v>62.9</v>
+        <v>24.66</v>
       </c>
       <c r="AH9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AI9" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AK9">
-        <v>60.41701473830908</v>
+        <v>56.40919021477925</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1606,43 +1690,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>99.19354838709677</v>
+        <v>98.38383838383838</v>
       </c>
       <c r="C10">
-        <v>181</v>
+        <v>477</v>
       </c>
       <c r="D10">
-        <v>138.1</v>
+        <v>334.32</v>
       </c>
       <c r="E10">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="F10">
-        <v>-0.2073071148049334</v>
+        <v>0.006761223449820727</v>
       </c>
       <c r="G10">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="H10">
-        <v>0.3004316358213446</v>
+        <v>-0.2675546464152112</v>
       </c>
       <c r="I10">
-        <v>131.3700012207031</v>
+        <v>334.3679931640625</v>
       </c>
       <c r="J10">
-        <v>130.2195014953613</v>
+        <v>322.0294982910156</v>
       </c>
       <c r="K10">
-        <v>122.2708009338379</v>
+        <v>325.2159979248047</v>
       </c>
       <c r="L10">
-        <v>99.26025043487549</v>
+        <v>272.7921491241455</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1666,49 +1750,49 @@
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>65.93000000000001</v>
+        <v>149.74</v>
       </c>
       <c r="Y10">
-        <v>138.47</v>
+        <v>369</v>
       </c>
       <c r="Z10">
-        <v>19.05</v>
+        <v>25.76</v>
       </c>
       <c r="AA10">
-        <v>-447.04</v>
+        <v>16.72</v>
       </c>
       <c r="AB10">
-        <v>144.88</v>
+        <v>117.07</v>
       </c>
       <c r="AC10">
-        <v>321.64</v>
+        <v>32.84</v>
       </c>
       <c r="AD10">
-        <v>7.94</v>
+        <v>44.5</v>
       </c>
       <c r="AE10">
-        <v>59.15</v>
+        <v>-43.67</v>
       </c>
       <c r="AF10">
-        <v>108.82</v>
+        <v>69.89</v>
       </c>
       <c r="AG10">
-        <v>26.87</v>
+        <v>38.81</v>
       </c>
       <c r="AH10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="AI10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AK10">
-        <v>60.13708399003179</v>
+        <v>55.32658245618253</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1716,43 +1800,43 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>97.78225806451613</v>
+        <v>90.30303030303031</v>
       </c>
       <c r="C11">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="D11">
-        <v>52.43</v>
+        <v>119.69</v>
       </c>
       <c r="E11">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="F11">
-        <v>0.823587449293069</v>
+        <v>0.7099284622311695</v>
       </c>
       <c r="G11">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="H11">
-        <v>0.1765339531241326</v>
+        <v>1.447154289929167</v>
       </c>
       <c r="I11">
-        <v>47.33999938964844</v>
+        <v>119.9020004272461</v>
       </c>
       <c r="J11">
-        <v>45.28199977874756</v>
+        <v>111.7780006408691</v>
       </c>
       <c r="K11">
-        <v>41.96300003051758</v>
+        <v>110.006600189209</v>
       </c>
       <c r="L11">
-        <v>36.49450012207031</v>
+        <v>92.19175010681153</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N11">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1776,49 +1860,49 @@
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>28.05</v>
+        <v>65.88</v>
       </c>
       <c r="Y11">
-        <v>52.65</v>
+        <v>127.75</v>
       </c>
       <c r="Z11">
-        <v>14.99</v>
+        <v>20.39</v>
       </c>
       <c r="AA11">
-        <v>120.04</v>
+        <v>171.43</v>
       </c>
       <c r="AB11">
-        <v>98.62</v>
+        <v>53.33</v>
       </c>
       <c r="AC11">
-        <v>331.71</v>
+        <v>109.71</v>
       </c>
       <c r="AD11">
-        <v>6.15</v>
+        <v>-207.94</v>
       </c>
       <c r="AE11">
-        <v>80.61</v>
+        <v>122.22</v>
       </c>
       <c r="AF11">
-        <v>-14.78</v>
+        <v>37.5</v>
       </c>
       <c r="AG11">
-        <v>180.49</v>
+        <v>30.1</v>
       </c>
       <c r="AH11" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AI11" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AK11">
-        <v>57.72195595287916</v>
+        <v>54.31048860750899</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1826,43 +1910,43 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>94.55645161290323</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="C12">
-        <v>378</v>
+        <v>461</v>
       </c>
       <c r="D12">
-        <v>442.14</v>
+        <v>469.01</v>
       </c>
       <c r="E12">
-        <v>2.54</v>
+        <v>1.66</v>
       </c>
       <c r="F12">
-        <v>-0.3271785757465617</v>
+        <v>-0.6447025418917229</v>
       </c>
       <c r="G12">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="H12">
-        <v>-0.9247787819621981</v>
+        <v>-0.5184876614899981</v>
       </c>
       <c r="I12">
-        <v>404.8220031738281</v>
+        <v>467.8200012207031</v>
       </c>
       <c r="J12">
-        <v>387.7849990844726</v>
+        <v>446.3899993896484</v>
       </c>
       <c r="K12">
-        <v>389.70419921875</v>
+        <v>436.1009997558594</v>
       </c>
       <c r="L12">
-        <v>372.411799621582</v>
+        <v>389.3027502441406</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1886,49 +1970,49 @@
         <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>293.26</v>
+        <v>253.86</v>
       </c>
       <c r="Y12">
-        <v>442.94</v>
+        <v>475.35</v>
       </c>
       <c r="Z12">
-        <v>62.28</v>
+        <v>32.27</v>
       </c>
       <c r="AA12">
-        <v>3.81</v>
+        <v>28.21</v>
       </c>
       <c r="AB12">
-        <v>34.3</v>
+        <v>49.1</v>
       </c>
       <c r="AC12">
-        <v>27.41</v>
+        <v>79.55</v>
       </c>
       <c r="AD12">
-        <v>20.97</v>
+        <v>7.97</v>
       </c>
       <c r="AE12">
-        <v>157.89</v>
+        <v>-6.32</v>
       </c>
       <c r="AF12">
-        <v>3.26</v>
+        <v>24.02</v>
       </c>
       <c r="AG12">
-        <v>-52.15</v>
+        <v>54.55</v>
       </c>
       <c r="AH12" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="AI12" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="AJ12" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK12">
-        <v>33.33205572256835</v>
+        <v>51.68292054894675</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1936,43 +2020,43 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>95.76612903225806</v>
+        <v>95.75757575757575</v>
       </c>
       <c r="C13">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="D13">
-        <v>101.06</v>
+        <v>112.98</v>
       </c>
       <c r="E13">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="F13">
-        <v>-1.166278802337959</v>
+        <v>-0.3655037853167757</v>
       </c>
       <c r="G13">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="H13">
-        <v>-0.2639911409103999</v>
+        <v>-0.002680908280713527</v>
       </c>
       <c r="I13">
-        <v>96.33000030517579</v>
+        <v>113.8419998168945</v>
       </c>
       <c r="J13">
-        <v>94.4435001373291</v>
+        <v>107.6559997558594</v>
       </c>
       <c r="K13">
-        <v>87.42980026245117</v>
+        <v>101.5178002929687</v>
       </c>
       <c r="L13">
-        <v>81.6258501625061</v>
+        <v>90.68095001220703</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1996,49 +2080,49 @@
         <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>61.93</v>
+        <v>58.04</v>
       </c>
       <c r="Y13">
-        <v>101.65</v>
+        <v>116.93</v>
       </c>
       <c r="Z13">
-        <v>22.9</v>
+        <v>19.06</v>
       </c>
       <c r="AA13">
-        <v>-0.08</v>
+        <v>26.51</v>
       </c>
       <c r="AB13">
-        <v>119.51</v>
+        <v>35.9</v>
       </c>
       <c r="AC13">
-        <v>6.1</v>
+        <v>108.04</v>
       </c>
       <c r="AD13">
-        <v>5.07</v>
+        <v>87.52</v>
       </c>
       <c r="AE13">
-        <v>135.14</v>
+        <v>14.78</v>
       </c>
       <c r="AF13">
-        <v>254.17</v>
+        <v>43.97</v>
       </c>
       <c r="AG13">
-        <v>-129.27</v>
+        <v>25.89</v>
       </c>
       <c r="AH13" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ13" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="AK13">
-        <v>32.08677581762093</v>
+        <v>50.34583568073575</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2046,61 +2130,61 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>94.95967741935483</v>
+        <v>96.36363636363636</v>
       </c>
       <c r="C14">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="D14">
-        <v>42.56</v>
+        <v>179.19</v>
       </c>
       <c r="E14">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="F14">
-        <v>-1.609803207821984</v>
+        <v>-0.7067467100194887</v>
       </c>
       <c r="G14">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="H14">
-        <v>-1.99855869867137</v>
+        <v>-0.8948871841021786</v>
       </c>
       <c r="I14">
-        <v>41.81600036621094</v>
+        <v>178.7700012207031</v>
       </c>
       <c r="J14">
-        <v>42.22910175323486</v>
+        <v>176.3420013427734</v>
       </c>
       <c r="K14">
-        <v>40.84085609436035</v>
+        <v>174.7008010864258</v>
       </c>
       <c r="L14">
-        <v>36.38011408805847</v>
+        <v>144.0074254226685</v>
       </c>
       <c r="M14">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2109,46 +2193,46 @@
         <v>1</v>
       </c>
       <c r="X14">
-        <v>27.71</v>
+        <v>94.72</v>
       </c>
       <c r="Y14">
-        <v>44.02</v>
+        <v>186.79</v>
       </c>
       <c r="Z14">
-        <v>40.37</v>
+        <v>33.22</v>
       </c>
       <c r="AA14">
-        <v>6.69</v>
+        <v>37.62</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>17.66</v>
       </c>
       <c r="AC14">
-        <v>233.33</v>
+        <v>54.04</v>
       </c>
       <c r="AD14">
-        <v>0.89</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AE14">
-        <v>-67.48</v>
+        <v>6.44</v>
       </c>
       <c r="AF14">
-        <v>200</v>
+        <v>36.26</v>
       </c>
       <c r="AG14">
-        <v>236.67</v>
+        <v>6.21</v>
       </c>
       <c r="AH14" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="AJ14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK14">
-        <v>30.51035633227886</v>
+        <v>49.60952046352062</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2156,43 +2240,43 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>98.99193548387096</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C15">
-        <v>57</v>
+        <v>324</v>
       </c>
       <c r="D15">
-        <v>35.63</v>
+        <v>60.03</v>
       </c>
       <c r="E15">
-        <v>2.91</v>
+        <v>1.46</v>
       </c>
       <c r="F15">
-        <v>0.1163458297374628</v>
+        <v>-0.851516435650943</v>
       </c>
       <c r="G15">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="H15">
-        <v>0.8097887757987725</v>
+        <v>-0.8251835688036266</v>
       </c>
       <c r="I15">
-        <v>32.696000289917</v>
+        <v>59.22400054931641</v>
       </c>
       <c r="J15">
-        <v>33.22550001144409</v>
+        <v>57.52649955749511</v>
       </c>
       <c r="K15">
-        <v>30.93640007019043</v>
+        <v>57.38799980163574</v>
       </c>
       <c r="L15">
-        <v>24.51910001754761</v>
+        <v>51.29625007629394</v>
       </c>
       <c r="M15">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2216,49 +2300,49 @@
         <v>1</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>15.55</v>
+        <v>34.11</v>
       </c>
       <c r="Y15">
-        <v>36.46</v>
+        <v>60.23</v>
       </c>
       <c r="Z15">
-        <v>10.08</v>
+        <v>14.84</v>
       </c>
       <c r="AA15">
-        <v>-5.24</v>
+        <v>20.66</v>
       </c>
       <c r="AB15">
-        <v>121.96</v>
+        <v>35.16</v>
       </c>
       <c r="AC15">
-        <v>2.94</v>
+        <v>61.67</v>
       </c>
       <c r="AD15">
-        <v>-67.64</v>
+        <v>4.8</v>
       </c>
       <c r="AE15">
-        <v>450</v>
+        <v>-3.96</v>
       </c>
       <c r="AF15">
-        <v>-136.14</v>
+        <v>14.77</v>
       </c>
       <c r="AG15">
-        <v>-18.63</v>
+        <v>46.67</v>
       </c>
       <c r="AH15" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="AI15" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="AJ15" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="AK15">
-        <v>28.10045096861539</v>
+        <v>46.98198052970811</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2266,43 +2350,43 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>97.17741935483872</v>
+        <v>96.96969696969697</v>
       </c>
       <c r="C16">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="D16">
-        <v>99.04000000000001</v>
+        <v>159.77</v>
       </c>
       <c r="E16">
-        <v>4.16</v>
+        <v>1.94</v>
       </c>
       <c r="F16">
-        <v>1.614739091507815</v>
+        <v>-0.3551630906288146</v>
       </c>
       <c r="G16">
-        <v>3.42</v>
+        <v>2.09</v>
       </c>
       <c r="H16">
-        <v>1.112649777947513</v>
+        <v>-0.07238452357926585</v>
       </c>
       <c r="I16">
-        <v>88.56866607666015</v>
+        <v>158.9539978027344</v>
       </c>
       <c r="J16">
-        <v>86.30324974060059</v>
+        <v>154.1555000305176</v>
       </c>
       <c r="K16">
-        <v>86.93760040283203</v>
+        <v>157.1318005371094</v>
       </c>
       <c r="L16">
-        <v>76.78002508163452</v>
+        <v>134.7600999832153</v>
       </c>
       <c r="M16">
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2326,49 +2410,49 @@
         <v>1</v>
       </c>
       <c r="W16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>51.93</v>
+        <v>82.06</v>
       </c>
       <c r="Y16">
-        <v>99.22</v>
+        <v>171.12</v>
       </c>
       <c r="Z16">
-        <v>25.4</v>
+        <v>42.71</v>
       </c>
       <c r="AA16">
-        <v>30.64</v>
+        <v>2.42</v>
       </c>
       <c r="AB16">
-        <v>11.05</v>
+        <v>17.33</v>
       </c>
       <c r="AC16">
-        <v>36</v>
+        <v>143.53</v>
       </c>
       <c r="AD16">
-        <v>-79.37</v>
+        <v>20.32</v>
       </c>
       <c r="AE16">
-        <v>8.57</v>
+        <v>10.11</v>
       </c>
       <c r="AF16">
-        <v>15.32</v>
+        <v>38.24</v>
       </c>
       <c r="AG16">
-        <v>17.34</v>
+        <v>60</v>
       </c>
       <c r="AH16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AI16" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AK16">
-        <v>27.77021072027784</v>
+        <v>44.94047796981175</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2376,49 +2460,49 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>99.39516129032258</v>
+        <v>92.92929292929293</v>
       </c>
       <c r="C17">
-        <v>93</v>
+        <v>299</v>
       </c>
       <c r="D17">
-        <v>68.90000000000001</v>
+        <v>643.22</v>
       </c>
       <c r="E17">
-        <v>4.26</v>
+        <v>2.21</v>
       </c>
       <c r="F17">
-        <v>1.734610552449443</v>
+        <v>-0.07596433405386741</v>
       </c>
       <c r="G17">
-        <v>3.85</v>
+        <v>2.44</v>
       </c>
       <c r="H17">
-        <v>1.704605373056416</v>
+        <v>0.4155407835105979</v>
       </c>
       <c r="I17">
-        <v>62.7140007019043</v>
+        <v>647.4320068359375</v>
       </c>
       <c r="J17">
-        <v>62.44550075531006</v>
+        <v>646.1645050048828</v>
       </c>
       <c r="K17">
-        <v>63.44144020080567</v>
+        <v>638.1826000976563</v>
       </c>
       <c r="L17">
-        <v>59.02305013656616</v>
+        <v>523.6037483215332</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2427,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -2436,49 +2520,49 @@
         <v>1</v>
       </c>
       <c r="W17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>32.23</v>
+        <v>357.69</v>
       </c>
       <c r="Y17">
-        <v>74.34999999999999</v>
+        <v>716.86</v>
       </c>
       <c r="Z17">
-        <v>60.04</v>
+        <v>173.4</v>
       </c>
       <c r="AA17">
-        <v>5920</v>
+        <v>10.89</v>
       </c>
       <c r="AB17">
-        <v>1.09</v>
+        <v>1.98</v>
       </c>
       <c r="AC17">
-        <v>80.3</v>
+        <v>1100</v>
       </c>
       <c r="AD17">
-        <v>24.9</v>
+        <v>2.34</v>
       </c>
       <c r="AE17">
-        <v>19</v>
+        <v>-42.86</v>
       </c>
       <c r="AF17">
-        <v>17.65</v>
+        <v>-72.56999999999999</v>
       </c>
       <c r="AG17">
-        <v>28.79</v>
+        <v>7557.14</v>
       </c>
       <c r="AH17" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="AJ17" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK17">
-        <v>21.20276076584865</v>
+        <v>44.84083775687444</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2486,109 +2570,1099 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>93.95161290322581</v>
+        <v>95.95959595959596</v>
       </c>
       <c r="C18">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="D18">
-        <v>28.98</v>
+        <v>157.36</v>
       </c>
       <c r="E18">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="F18">
-        <v>0.368075897714882</v>
+        <v>0.575499431287676</v>
       </c>
       <c r="G18">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="H18">
-        <v>-0.7458154625106695</v>
+        <v>0.4713036757494395</v>
       </c>
       <c r="I18">
-        <v>27.68200035095215</v>
+        <v>159.7359985351563</v>
       </c>
       <c r="J18">
-        <v>28.12200002670288</v>
+        <v>152.8514991760254</v>
       </c>
       <c r="K18">
-        <v>26.9446000289917</v>
+        <v>149.2073992919922</v>
       </c>
       <c r="L18">
-        <v>26.27824999809265</v>
+        <v>137.6006999969482</v>
       </c>
       <c r="M18">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
+        <v>1.07</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="Y18">
+        <v>163.02</v>
+      </c>
+      <c r="Z18">
+        <v>125.58</v>
+      </c>
+      <c r="AA18">
+        <v>26.49</v>
+      </c>
+      <c r="AB18">
+        <v>24.9</v>
+      </c>
+      <c r="AC18">
+        <v>54.47</v>
+      </c>
+      <c r="AD18">
+        <v>13.98</v>
+      </c>
+      <c r="AE18">
+        <v>0.53</v>
+      </c>
+      <c r="AF18">
+        <v>30.34</v>
+      </c>
+      <c r="AG18">
+        <v>17.89</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK18">
+        <v>43.37517046028525</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19">
+        <v>94.54545454545455</v>
+      </c>
+      <c r="C19">
+        <v>491</v>
+      </c>
+      <c r="D19">
+        <v>2096.39</v>
+      </c>
+      <c r="E19">
+        <v>2.09</v>
+      </c>
+      <c r="F19">
+        <v>-0.2000526703093996</v>
+      </c>
+      <c r="G19">
+        <v>1.53</v>
+      </c>
+      <c r="H19">
+        <v>-0.8530650149230474</v>
+      </c>
+      <c r="I19">
+        <v>2078.389990234375</v>
+      </c>
+      <c r="J19">
+        <v>2009.068499755859</v>
+      </c>
+      <c r="K19">
+        <v>1907.710400390625</v>
+      </c>
+      <c r="L19">
+        <v>1627.680047607422</v>
+      </c>
+      <c r="M19">
         <v>1.03</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="b">
-        <v>1</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>19.42</v>
-      </c>
-      <c r="Y18">
-        <v>30.92</v>
-      </c>
-      <c r="Z18">
-        <v>15.35</v>
-      </c>
-      <c r="AA18">
-        <v>3.51</v>
-      </c>
-      <c r="AB18">
-        <v>13.87</v>
-      </c>
-      <c r="AC18">
-        <v>6.06</v>
-      </c>
-      <c r="AD18">
-        <v>-206.12</v>
-      </c>
-      <c r="AE18">
-        <v>-38.6</v>
-      </c>
-      <c r="AF18">
-        <v>83.87</v>
-      </c>
-      <c r="AG18">
-        <v>-6.06</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ18" t="s">
+      <c r="N19">
+        <v>1.09</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1111.71</v>
+      </c>
+      <c r="Y19">
+        <v>2110</v>
+      </c>
+      <c r="Z19">
+        <v>39.27</v>
+      </c>
+      <c r="AA19">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB19">
+        <v>12.58</v>
+      </c>
+      <c r="AC19">
+        <v>73.22</v>
+      </c>
+      <c r="AD19">
+        <v>-26.13</v>
+      </c>
+      <c r="AE19">
+        <v>-26.79</v>
+      </c>
+      <c r="AF19">
+        <v>33.08</v>
+      </c>
+      <c r="AG19">
+        <v>77.8</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK19">
+        <v>39.43470282609156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>97.37373737373738</v>
+      </c>
+      <c r="C20">
+        <v>414</v>
+      </c>
+      <c r="D20">
+        <v>226.73</v>
+      </c>
+      <c r="E20">
+        <v>1.25</v>
+      </c>
+      <c r="F20">
+        <v>-1.068671024098124</v>
+      </c>
+      <c r="G20">
+        <v>1.45</v>
+      </c>
+      <c r="H20">
+        <v>-0.9645907994007307</v>
+      </c>
+      <c r="I20">
+        <v>224.4040008544922</v>
+      </c>
+      <c r="J20">
+        <v>214.8070007324219</v>
+      </c>
+      <c r="K20">
+        <v>204.3055999755859</v>
+      </c>
+      <c r="L20">
+        <v>173.0658498001099</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>1.1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>106.56</v>
+      </c>
+      <c r="Y20">
+        <v>228.84</v>
+      </c>
+      <c r="Z20">
+        <v>23.59</v>
+      </c>
+      <c r="AA20">
+        <v>12.04</v>
+      </c>
+      <c r="AB20">
+        <v>17.47</v>
+      </c>
+      <c r="AC20">
+        <v>19.49</v>
+      </c>
+      <c r="AD20">
+        <v>5.91</v>
+      </c>
+      <c r="AE20">
+        <v>12.8</v>
+      </c>
+      <c r="AF20">
+        <v>-18.83</v>
+      </c>
+      <c r="AG20">
+        <v>30.51</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK20">
+        <v>33.86758482876203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21">
+        <v>96.76767676767678</v>
+      </c>
+      <c r="C21">
+        <v>447</v>
+      </c>
+      <c r="D21">
+        <v>668.45</v>
+      </c>
+      <c r="E21">
+        <v>4.77</v>
+      </c>
+      <c r="F21">
+        <v>2.57125350606415</v>
+      </c>
+      <c r="G21">
+        <v>3.42</v>
+      </c>
+      <c r="H21">
+        <v>1.781731643362216</v>
+      </c>
+      <c r="I21">
+        <v>679.7260131835938</v>
+      </c>
+      <c r="J21">
+        <v>656.2610076904297</v>
+      </c>
+      <c r="K21">
+        <v>656.6260046386719</v>
+      </c>
+      <c r="L21">
+        <v>558.9589010620117</v>
+      </c>
+      <c r="M21">
+        <v>1.04</v>
+      </c>
+      <c r="N21">
+        <v>1.04</v>
+      </c>
+      <c r="P21">
+        <v>5</v>
+      </c>
+      <c r="Q21">
+        <v>3</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>328.9</v>
+      </c>
+      <c r="Y21">
+        <v>725.4</v>
+      </c>
+      <c r="Z21">
+        <v>33.77</v>
+      </c>
+      <c r="AA21">
+        <v>23.72</v>
+      </c>
+      <c r="AB21">
+        <v>4.15</v>
+      </c>
+      <c r="AC21">
+        <v>34.21</v>
+      </c>
+      <c r="AD21">
+        <v>4.94</v>
+      </c>
+      <c r="AE21">
+        <v>0.49</v>
+      </c>
+      <c r="AF21">
+        <v>4.64</v>
+      </c>
+      <c r="AG21">
+        <v>27.63</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK21">
+        <v>28.93792010222845</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>94.14141414141413</v>
+      </c>
+      <c r="C22">
+        <v>343</v>
+      </c>
+      <c r="D22">
+        <v>108.51</v>
+      </c>
+      <c r="E22">
+        <v>1.84</v>
+      </c>
+      <c r="F22">
+        <v>-0.4585700375084246</v>
+      </c>
+      <c r="G22">
+        <v>1.88</v>
+      </c>
+      <c r="H22">
+        <v>-0.365139707833184</v>
+      </c>
+      <c r="I22">
+        <v>108.2220016479492</v>
+      </c>
+      <c r="J22">
+        <v>104.2419994354248</v>
+      </c>
+      <c r="K22">
+        <v>103.2587994384766</v>
+      </c>
+      <c r="L22">
+        <v>92.87759998321533</v>
+      </c>
+      <c r="M22">
+        <v>1.04</v>
+      </c>
+      <c r="N22">
+        <v>1.05</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>58.74</v>
+      </c>
+      <c r="Y22">
+        <v>109.56</v>
+      </c>
+      <c r="Z22">
+        <v>33.14</v>
+      </c>
+      <c r="AA22">
+        <v>17.34</v>
+      </c>
+      <c r="AB22">
+        <v>5.07</v>
+      </c>
+      <c r="AC22">
+        <v>38.3</v>
+      </c>
+      <c r="AD22">
+        <v>5.46</v>
+      </c>
+      <c r="AE22">
+        <v>-1.52</v>
+      </c>
+      <c r="AF22">
+        <v>67.09</v>
+      </c>
+      <c r="AG22">
+        <v>-15.96</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK22">
+        <v>26.86482766423576</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23">
+        <v>92.72727272727272</v>
+      </c>
+      <c r="C23">
+        <v>188</v>
+      </c>
+      <c r="D23">
+        <v>168.36</v>
+      </c>
+      <c r="E23">
+        <v>1.11</v>
+      </c>
+      <c r="F23">
+        <v>-1.213440749729578</v>
+      </c>
+      <c r="G23">
+        <v>1.17</v>
+      </c>
+      <c r="H23">
+        <v>-1.354931045072622</v>
+      </c>
+      <c r="I23">
+        <v>167.1379974365234</v>
+      </c>
+      <c r="J23">
+        <v>161.7634986877441</v>
+      </c>
+      <c r="K23">
+        <v>153.9375994873047</v>
+      </c>
+      <c r="L23">
+        <v>130.8318496704102</v>
+      </c>
+      <c r="M23">
+        <v>1.03</v>
+      </c>
+      <c r="N23">
+        <v>1.09</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>93.08</v>
+      </c>
+      <c r="Y23">
+        <v>169.93</v>
+      </c>
+      <c r="Z23">
+        <v>95.95</v>
+      </c>
+      <c r="AA23">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AB23">
+        <v>1.14</v>
+      </c>
+      <c r="AC23">
+        <v>164.86</v>
+      </c>
+      <c r="AD23">
+        <v>2.17</v>
+      </c>
+      <c r="AE23">
+        <v>20.99</v>
+      </c>
+      <c r="AF23">
+        <v>62</v>
+      </c>
+      <c r="AG23">
+        <v>35.14</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK23">
+        <v>26.80607030843395</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>90.1010101010101</v>
+      </c>
+      <c r="C24">
+        <v>400</v>
+      </c>
+      <c r="D24">
+        <v>374.56</v>
+      </c>
+      <c r="E24">
+        <v>1.01</v>
+      </c>
+      <c r="F24">
+        <v>-1.316847696609188</v>
+      </c>
+      <c r="G24">
+        <v>1.29</v>
+      </c>
+      <c r="H24">
+        <v>-1.187642368356097</v>
+      </c>
+      <c r="I24">
+        <v>371.8119934082031</v>
+      </c>
+      <c r="J24">
+        <v>357.8624984741211</v>
+      </c>
+      <c r="K24">
+        <v>340.8323986816406</v>
+      </c>
+      <c r="L24">
+        <v>306.5521007537842</v>
+      </c>
+      <c r="M24">
+        <v>1.04</v>
+      </c>
+      <c r="N24">
+        <v>1.09</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>212.22</v>
+      </c>
+      <c r="Y24">
+        <v>377.36</v>
+      </c>
+      <c r="Z24">
+        <v>52.23</v>
+      </c>
+      <c r="AA24">
+        <v>2.27</v>
+      </c>
+      <c r="AB24">
+        <v>2.82</v>
+      </c>
+      <c r="AC24">
+        <v>51.5</v>
+      </c>
+      <c r="AD24">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="AE24">
+        <v>27.78</v>
+      </c>
+      <c r="AF24">
+        <v>-10.41</v>
+      </c>
+      <c r="AG24">
+        <v>32.34</v>
+      </c>
+      <c r="AH24" t="s">
         <v>77</v>
       </c>
-      <c r="AK18">
-        <v>17.61740566270545</v>
+      <c r="AI24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK24">
+        <v>23.44060044750043</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>95.55555555555556</v>
+      </c>
+      <c r="C25">
+        <v>419</v>
+      </c>
+      <c r="D25">
+        <v>229.44</v>
+      </c>
+      <c r="E25">
+        <v>1.14</v>
+      </c>
+      <c r="F25">
+        <v>-1.182418665665695</v>
+      </c>
+      <c r="G25">
+        <v>1.27</v>
+      </c>
+      <c r="H25">
+        <v>-1.215523814475518</v>
+      </c>
+      <c r="I25">
+        <v>227.4040008544922</v>
+      </c>
+      <c r="J25">
+        <v>219.982999420166</v>
+      </c>
+      <c r="K25">
+        <v>210.3126000976563</v>
+      </c>
+      <c r="L25">
+        <v>182.9231498718262</v>
+      </c>
+      <c r="M25">
+        <v>1.03</v>
+      </c>
+      <c r="N25">
+        <v>1.08</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>122.15</v>
+      </c>
+      <c r="Y25">
+        <v>231.63</v>
+      </c>
+      <c r="Z25">
+        <v>21.52</v>
+      </c>
+      <c r="AA25">
+        <v>7.02</v>
+      </c>
+      <c r="AB25">
+        <v>6.27</v>
+      </c>
+      <c r="AC25">
+        <v>1.39</v>
+      </c>
+      <c r="AD25">
+        <v>1.43</v>
+      </c>
+      <c r="AE25">
+        <v>-61.17</v>
+      </c>
+      <c r="AF25">
+        <v>370</v>
+      </c>
+      <c r="AG25">
+        <v>-44.44</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK25">
+        <v>12.25877082879282</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26">
+        <v>91.71717171717172</v>
+      </c>
+      <c r="C26">
+        <v>338</v>
+      </c>
+      <c r="D26">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="E26">
+        <v>2.42</v>
+      </c>
+      <c r="F26">
+        <v>0.1411902543933137</v>
+      </c>
+      <c r="G26">
+        <v>1.97</v>
+      </c>
+      <c r="H26">
+        <v>-0.2396732002957904</v>
+      </c>
+      <c r="I26">
+        <v>70.79000091552734</v>
+      </c>
+      <c r="J26">
+        <v>65.7295000076294</v>
+      </c>
+      <c r="K26">
+        <v>63.62380004882812</v>
+      </c>
+      <c r="L26">
+        <v>58.85530000686646</v>
+      </c>
+      <c r="M26">
+        <v>1.08</v>
+      </c>
+      <c r="N26">
+        <v>1.11</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>40.87</v>
+      </c>
+      <c r="Y26">
+        <v>72.11</v>
+      </c>
+      <c r="Z26">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="AA26">
+        <v>66.63</v>
+      </c>
+      <c r="AB26">
+        <v>106.56</v>
+      </c>
+      <c r="AC26">
+        <v>66.34</v>
+      </c>
+      <c r="AD26">
+        <v>10.92</v>
+      </c>
+      <c r="AE26">
+        <v>38.84</v>
+      </c>
+      <c r="AF26">
+        <v>6.14</v>
+      </c>
+      <c r="AG26">
+        <v>12.87</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AK26">
+        <v>58.3192005606622</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27">
+        <v>93.13131313131314</v>
+      </c>
+      <c r="C27">
+        <v>168</v>
+      </c>
+      <c r="D27">
+        <v>47.72</v>
+      </c>
+      <c r="E27">
+        <v>1.49</v>
+      </c>
+      <c r="F27">
+        <v>-0.82049435158706</v>
+      </c>
+      <c r="G27">
+        <v>1.44</v>
+      </c>
+      <c r="H27">
+        <v>-0.9785315224604411</v>
+      </c>
+      <c r="I27">
+        <v>46.98880081176758</v>
+      </c>
+      <c r="J27">
+        <v>46.28180027008057</v>
+      </c>
+      <c r="K27">
+        <v>44.92664001464843</v>
+      </c>
+      <c r="L27">
+        <v>39.52371994018554</v>
+      </c>
+      <c r="M27">
+        <v>1.02</v>
+      </c>
+      <c r="N27">
+        <v>1.05</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>27.63</v>
+      </c>
+      <c r="Y27">
+        <v>47.91</v>
+      </c>
+      <c r="Z27">
+        <v>4.67</v>
+      </c>
+      <c r="AA27">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AB27">
+        <v>3</v>
+      </c>
+      <c r="AC27">
+        <v>68.97</v>
+      </c>
+      <c r="AD27">
+        <v>11.1</v>
+      </c>
+      <c r="AE27">
+        <v>-38.94</v>
+      </c>
+      <c r="AF27">
+        <v>105.77</v>
+      </c>
+      <c r="AG27">
+        <v>34.48</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK27">
+        <v>26.41109916787278</v>
       </c>
     </row>
   </sheetData>
